--- a/artfynd/A 50902-2019 artfynd.xlsx
+++ b/artfynd/A 50902-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50902-2019 artfynd.xlsx
+++ b/artfynd/A 50902-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,327 +1141,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112606407</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78422</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Nordanås, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>648727</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7131449</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112606406</v>
-      </c>
-      <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Volmsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>648605</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7131569</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112606405</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78422</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Nordanås, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>648622</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7131592</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
